--- a/artfynd/A 30777-2023 artfynd.xlsx
+++ b/artfynd/A 30777-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30777-2023 artfynd.xlsx
+++ b/artfynd/A 30777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127800199</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bollebygd, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>357553</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6393624</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Källman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30777-2023 artfynd.xlsx
+++ b/artfynd/A 30777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72066757</v>
+        <v>99176529</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väg 1629, Vg</t>
+          <t>Väg 1629 mot Seglora, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357492.8650146219</v>
+        <v>357740</v>
       </c>
       <c r="R2" t="n">
-        <v>6393660.189176183</v>
+        <v>6393489</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På avverkat virke.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114002958</v>
+        <v>127800230</v>
       </c>
       <c r="B3" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,46 +792,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bollebygd, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357613</v>
+        <v>357839</v>
       </c>
       <c r="R3" t="n">
-        <v>6393594</v>
+        <v>6393470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,19 +875,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -918,7 +896,7 @@
         <v>127800199</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,6 +997,640 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72066757</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väg 1629, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>357493</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6393660</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-06-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-06-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114002957</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bollebygd, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>357668</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6393543</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114002958</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bollebygd, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>357613</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6393594</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114002960</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bollebygd, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>357501</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6393663</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129949583</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>357553</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6393646</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129949584</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>357572</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6393634</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30777-2023 artfynd.xlsx
+++ b/artfynd/A 30777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127800199</v>
+        <v>134599878</v>
       </c>
       <c r="B4" t="n">
-        <v>5199</v>
+        <v>58131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,16 +922,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bollebygd, Vg</t>
+          <t>Bollebygd och Härryda kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357553</v>
+        <v>357794</v>
       </c>
       <c r="R4" t="n">
-        <v>6393624</v>
+        <v>6393440</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Källman</t>
+          <t>Sandra Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Källman</t>
+          <t>Sandra Johansson, Andreas Källman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72066757</v>
+        <v>127800199</v>
       </c>
       <c r="B5" t="n">
-        <v>99156</v>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,49 +1006,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väg 1629, Vg</t>
+          <t>Bollebygd, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357493</v>
+        <v>357553</v>
       </c>
       <c r="R5" t="n">
-        <v>6393660</v>
+        <v>6393624</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,12 +1060,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,26 +1084,25 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tobias Federsel</t>
+          <t>Andreas Källman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114002957</v>
+        <v>72066757</v>
       </c>
       <c r="B6" t="n">
         <v>99156</v>
@@ -1143,27 +1135,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bollebygd, Vg</t>
+          <t>Väg 1629, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357668</v>
+        <v>357493</v>
       </c>
       <c r="R6" t="n">
-        <v>6393543</v>
+        <v>6393660</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,12 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114002958</v>
+        <v>114002957</v>
       </c>
       <c r="B7" t="n">
         <v>99156</v>
@@ -1250,7 +1242,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357613</v>
+        <v>357668</v>
       </c>
       <c r="R7" t="n">
-        <v>6393594</v>
+        <v>6393543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114002960</v>
+        <v>114002958</v>
       </c>
       <c r="B8" t="n">
         <v>99156</v>
@@ -1360,7 +1352,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1377,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357501</v>
+        <v>357613</v>
       </c>
       <c r="R8" t="n">
-        <v>6393663</v>
+        <v>6393594</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129949583</v>
+        <v>114002960</v>
       </c>
       <c r="B9" t="n">
         <v>99156</v>
@@ -1468,20 +1460,32 @@
           <t>(Custer) Rchb.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bollebygd kommun, Vg</t>
+          <t>Bollebygd, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357553</v>
+        <v>357501</v>
       </c>
       <c r="R9" t="n">
-        <v>6393646</v>
+        <v>6393663</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,12 +1509,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,25 +1523,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sandra Johansson</t>
+          <t>Tobias Federsel</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Elin Eriksson</t>
+          <t>Tobias Federsel</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129949584</v>
+        <v>129949583</v>
       </c>
       <c r="B10" t="n">
         <v>99156</v>
@@ -1572,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357572</v>
+        <v>357553</v>
       </c>
       <c r="R10" t="n">
-        <v>6393634</v>
+        <v>6393646</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1631,6 +1636,103 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129949584</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>357572</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6393634</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30777-2023 artfynd.xlsx
+++ b/artfynd/A 30777-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99176529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127800230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134599878</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127800199</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72066757</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114002957</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114002958</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114002960</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949583</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1733,8 +1783,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949584</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>